--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_25_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_25_7.xlsx
@@ -513,441 +513,441 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_10</t>
+          <t>model_25_7_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9865390346310713</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8524151061981063</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9918507186121369</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9847913306822722</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9896726971709457</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09001353740407221</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9869008644192128</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1030175845004446</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2111293584940264</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1570735781129646</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2205232661176294</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3000225614917522</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N2" t="n">
-        <v>1.00461518812649</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3127951430667769</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P2" t="n">
-        <v>192.8155904087247</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q2" t="n">
-        <v>307.3899179463356</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_9</t>
+          <t>model_25_7_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9854330307441874</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8523428917766919</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9909286669816556</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9865371650591139</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9900862532053321</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09740939048834481</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9873837625877282</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1146735241147466</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1868933859497509</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1507835789576654</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L3" t="n">
-        <v>0.23908109305887</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3121047748566895</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N3" t="n">
-        <v>1.004994389459136</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3253917212682892</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P3" t="n">
-        <v>192.6576653227926</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q3" t="n">
-        <v>307.2319928604034</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_11</t>
+          <t>model_25_7_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9871947756972577</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8521361584835598</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9921364589193903</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E4" t="n">
-        <v>0.983082351749706</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9890115274691921</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08562859387507409</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9887661890708213</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0994054529704802</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2348536974335217</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1671296685088193</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2126273496069134</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2926236386129358</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N4" t="n">
-        <v>1.004390362618083</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3050812327231276</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P4" t="n">
-        <v>192.9154720220338</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q4" t="n">
-        <v>307.4897995596447</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_8</t>
+          <t>model_25_7_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9837396605104816</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8517883604961243</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9891537053987545</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9882986681808377</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9901525355125097</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1087329650383884</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9910919158142656</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1371113620232385</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1624398971990114</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1497754552174879</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2596052641532947</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M5" t="n">
-        <v>0.329746819603144</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N5" t="n">
-        <v>1.005574973539263</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3437848243836675</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P5" t="n">
-        <v>192.4377205292167</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q5" t="n">
-        <v>307.0120480668276</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_12</t>
+          <t>model_25_7_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9875091014997938</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8516077627392881</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9919562912117224</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9814261570076475</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9881808272488545</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08352669578617791</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9922995738458052</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1016830086426378</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J6" t="n">
-        <v>0.257845277178399</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1797642409724592</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2076264507095072</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M6" t="n">
-        <v>0.289009854133346</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N6" t="n">
-        <v>1.004282593771499</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3013136019566764</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P6" t="n">
-        <v>192.9651779764152</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q6" t="n">
-        <v>307.539505514026</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_13</t>
+          <t>model_25_7_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9875681963734027</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8509086522565583</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9914430552898289</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9798350400172936</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9872414234228352</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08313152809424858</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9969745288629266</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1081709825431422</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2799334364015592</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1940521458289676</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2030826942614379</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2883253857957162</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N7" t="n">
-        <v>1.004262332671976</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O7" t="n">
-        <v>0.300599994384869</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P7" t="n">
-        <v>192.9746624992501</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q7" t="n">
-        <v>307.548990036861</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_7</t>
+          <t>model_25_7_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9812882039067783</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8505840732453912</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9862535603162524</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9900500152027697</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.989746568062748</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G8" t="n">
-        <v>0.125125866635272</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.99914499020515</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1737729922800069</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1381273971691822</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1559500354527139</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2822808768791754</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3537313481093696</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N8" t="n">
-        <v>1.006415472946247</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3687904239232216</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P8" t="n">
-        <v>192.1568702304294</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q8" t="n">
-        <v>306.7311977680403</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_14</t>
+          <t>model_25_7_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9874400186856587</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C9" t="n">
-        <v>0.850099213108954</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D9" t="n">
-        <v>0.990699464032902</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9783179817024071</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9862401000678749</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08398865288239683</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.002387252170082</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1175709494234537</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3009935003774818</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2092818185533104</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1989583332695518</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2898079586250123</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N9" t="n">
-        <v>1.004306279307774</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O9" t="n">
-        <v>0.302145683408857</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P9" t="n">
-        <v>192.9541471479939</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q9" t="n">
-        <v>307.5284746856047</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="10">
@@ -957,932 +957,932 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9871776034537281</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8492251826033784</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9898042119914348</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E10" t="n">
-        <v>0.976880872637425</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9852121887915334</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08574342474662741</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.008231898185406</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1288881071508093</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3209436951405419</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2249158814669481</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1952211938602297</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2928197820274911</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N10" t="n">
-        <v>1.004396250244436</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3052857263689133</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P10" t="n">
-        <v>192.9127917504314</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q10" t="n">
-        <v>307.4871192880423</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_6</t>
+          <t>model_25_7_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9778670183139553</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8485178185018004</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9818909311681125</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E11" t="n">
-        <v>0.991759019561298</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9887135059273475</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1480033504475911</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01296204518977</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2289223355806266</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1144027052621137</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1716624405894978</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3072827826813359</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3847120357456875</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N11" t="n">
-        <v>1.007588450863787</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4010900235710821</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P11" t="n">
-        <v>191.8210407346297</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q11" t="n">
-        <v>306.3953682722405</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_16</t>
+          <t>model_25_7_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9868221851349825</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8483210845162611</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9888170758154669</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9755271452644791</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F12" t="n">
-        <v>0.984184169596214</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08812010868062964</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.014277606256949</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1413668006185151</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3397363709397779</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2405515857791465</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1918401827018698</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2968503135936185</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N12" t="n">
-        <v>1.00451810795372</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3094878460081613</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P12" t="n">
-        <v>192.8581090474468</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q12" t="n">
-        <v>307.4324365850576</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_17</t>
+          <t>model_25_7_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9864057189252986</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8474124409181871</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9877830075533905</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9742582570191525</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9831753732313928</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09090502014243683</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.020353710181188</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1544387770907377</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3573512954042193</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2558949195839836</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1887767997904525</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3015045938993912</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N13" t="n">
-        <v>1.004660896368469</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3143402686622392</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P13" t="n">
-        <v>192.7958801044683</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q13" t="n">
-        <v>307.3702076420792</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_18</t>
+          <t>model_25_7_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9859526813985178</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8465180810126857</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9867354351683532</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9730743256779318</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F14" t="n">
-        <v>0.982199720852012</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09393448417006627</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.026334298987425</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1676814633546642</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3737868335404527</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2707341484475585</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1860067463232513</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3064873311738452</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N14" t="n">
-        <v>1.004816223520508</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3195351313781548</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P14" t="n">
-        <v>192.7303154332553</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q14" t="n">
-        <v>307.3046429708661</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_19</t>
+          <t>model_25_7_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9854814899711316</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8456511327849413</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9856985302628635</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9719737107458496</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9812665251144452</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09708534341463498</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.032131585778281</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1807892987129208</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3890657589812614</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2849276311027782</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1835071100478828</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3115852105197469</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N15" t="n">
-        <v>1.004977774867041</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3248500380018766</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P15" t="n">
-        <v>192.6643297165691</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q15" t="n">
-        <v>307.23865725418</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_5</t>
+          <t>model_25_7_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9732168137626984</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8453233146281766</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9756559121830414</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9933869540334647</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9868653288828725</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1790992896940685</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.034323707302031</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I16" t="n">
-        <v>0.307741137458429</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J16" t="n">
-        <v>0.09180343943560142</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1997723726954128</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3347960672862997</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4232012401849368</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N16" t="n">
-        <v>1.009182806709932</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4412177931269473</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P16" t="n">
-        <v>191.4396298717946</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q16" t="n">
-        <v>306.0139574094054</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_20</t>
+          <t>model_25_7_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9850059898015397</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8448207737922983</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9846896878997079</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9709541254343572</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9803819932847939</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G17" t="n">
-        <v>0.100265015238172</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.037684200185536</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1935423868010054</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4032198173178705</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2983809578559413</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1812502106463608</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3166465146471251</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N17" t="n">
-        <v>1.005140803496615</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3301268123243011</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P17" t="n">
-        <v>192.5998768921484</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q17" t="n">
-        <v>307.1742044297592</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_21</t>
+          <t>model_25_7_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9845364777918526</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8440329220012267</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9837210059340407</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9700125773809847</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9795497137100382</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G18" t="n">
-        <v>0.103404644208854</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.042952568740156</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2057877948931594</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4162905490398186</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3110395515818309</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L18" t="n">
-        <v>0.179208505889953</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3215659251364391</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N18" t="n">
-        <v>1.005301779042793</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3352556523027289</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P18" t="n">
-        <v>192.5382108058744</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q18" t="n">
-        <v>307.1125383434853</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_22</t>
+          <t>model_25_7_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9840801328630988</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8432910763181058</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9828000989221862</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E19" t="n">
-        <v>0.969145398904628</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9787713052215342</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1064562248487063</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04791329423907</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2174292650296625</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4283288695258584</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3228787905919275</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1773701058466441</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3262763013899512</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N19" t="n">
-        <v>1.005458240161223</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O19" t="n">
-        <v>0.340166559025176</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P19" t="n">
-        <v>192.4800428252297</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q19" t="n">
-        <v>307.0543703628405</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_23</t>
+          <t>model_25_7_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9836421335958844</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8425968866698298</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9819318735121306</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9683486886925942</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9780468789696892</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G20" t="n">
-        <v>0.10938512796537</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.052555343613542</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2284047707569587</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J20" t="n">
-        <v>0.439388937468573</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3338969843391005</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1757158454188848</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3307342255729969</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N20" t="n">
-        <v>1.005608411338554</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3448142662698691</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P20" t="n">
-        <v>192.4257606801016</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q20" t="n">
-        <v>307.0000882177125</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_24</t>
+          <t>model_25_7_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9832257563579986</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8419505978620967</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9811186261213404</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9676182149349084</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9773755472155544</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1121694444723533</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.056877079846739</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2386852823521614</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4495294995805487</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3441076349289284</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L21" t="n">
-        <v>0.174214858097043</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3349170710375231</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N21" t="n">
-        <v>1.005751169248686</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3491751841255041</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P21" t="n">
-        <v>192.3754893077765</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q21" t="n">
-        <v>306.9498168453874</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_4</t>
+          <t>model_25_7_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9670242082629429</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8406707724411526</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9670641105241951</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9948868476932216</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9839793358404603</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2205092711852605</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.065435278329647</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4163527574620619</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J22" t="n">
-        <v>0.07098165814901559</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2436670140247534</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3651982127344815</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4695841470761769</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N22" t="n">
-        <v>1.01130598573842</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4895753163904012</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P22" t="n">
-        <v>191.023631077575</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q22" t="n">
-        <v>305.5979586151858</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_3</t>
+          <t>model_25_7_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.95891722183507</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8341592976186544</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9555642242831792</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9962031392330234</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9798010017300324</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2747207267576866</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.108977540450277</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5617263733914052</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0527086730124711</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3072175751092924</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L23" t="n">
-        <v>0.398875276413722</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5241380798584344</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N23" t="n">
-        <v>1.014085523942262</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5464517230334085</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P23" t="n">
-        <v>190.5840004727754</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q23" t="n">
-        <v>305.1583280103862</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_2</t>
+          <t>model_25_7_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9484632197577278</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8253134485089333</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9405608954125777</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9972695216619062</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9740527065629266</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3446266867851269</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.168129774178372</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7513880903149457</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0379049690581156</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3946465296865307</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4359009665246458</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5870491348985423</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N24" t="n">
-        <v>1.017669753225922</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6120410319304109</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P24" t="n">
-        <v>190.1305870301955</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q24" t="n">
-        <v>304.7049145678063</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_1</t>
+          <t>model_25_7_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9351712252533413</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8135855774437436</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9214550719049562</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9980082172747694</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9664499849243376</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4335103152399667</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.246554101993176</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9929107097913473</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J25" t="n">
-        <v>0.02765026974103696</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5102804673115976</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4761726712319985</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6584150022895641</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N25" t="n">
-        <v>1.022227008484569</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O25" t="n">
-        <v>0.68644509204398</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P25" t="n">
-        <v>189.6716793755935</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q25" t="n">
-        <v>304.2460069132043</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_25_7_0</t>
+          <t>model_25_7_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9184893285754476</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7983618385644773</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8976851507520517</v>
+        <v>0.9994736602017712</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9983280245205672</v>
+        <v>0.9996107523118349</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9567178274241106</v>
+        <v>0.99960440657317</v>
       </c>
       <c r="G26" t="n">
-        <v>0.545062235138113</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.348355313977702</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I26" t="n">
-        <v>1.293393629007414</v>
+        <v>0.0002528621332423948</v>
       </c>
       <c r="J26" t="n">
-        <v>0.02321065065034434</v>
+        <v>0.0002369542542420439</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6583021557062597</v>
+        <v>0.0002449081937422194</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5208440545425662</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7382833027626408</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N26" t="n">
-        <v>1.027946515916989</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7697135514183697</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P26" t="n">
-        <v>189.2137105958489</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q26" t="n">
-        <v>303.7880381334597</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
   </sheetData>
